--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488075_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488075_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>J. MUNOZ LEIVA</t>
+          <t>P. RODRIGUEZ SANCHEZ</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.4011</v>
+        <v>5.4913</v>
       </c>
       <c r="E2" t="n">
-        <v>3.4803</v>
+        <v>4.3188</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9209000000000001</v>
+        <v>1.1725</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1085</v>
+        <v>2.8291</v>
       </c>
       <c r="H2" t="n">
-        <v>1.5016</v>
+        <v>0.715</v>
       </c>
       <c r="I2" t="n">
-        <v>-1.393</v>
+        <v>2.1141</v>
       </c>
       <c r="J2" t="n">
-        <v>0.3831</v>
+        <v>3.9029</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0616</v>
+        <v>0.7534999999999999</v>
       </c>
       <c r="L2" t="n">
-        <v>0.3214</v>
+        <v>3.1494</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.2745</v>
+        <v>-1.0738</v>
       </c>
       <c r="N2" t="n">
-        <v>1.4399</v>
+        <v>-0.0385</v>
       </c>
       <c r="O2" t="n">
-        <v>-1.7144</v>
+        <v>-1.0353</v>
       </c>
       <c r="P2" t="n">
-        <v>2.3787</v>
+        <v>1.784</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>-0.9911</v>
       </c>
       <c r="R2" t="n">
-        <v>2.3787</v>
+        <v>2.7751</v>
       </c>
       <c r="S2" t="n">
-        <v>1.8435</v>
+        <v>-0.5955</v>
       </c>
       <c r="T2" t="n">
-        <v>1.9605</v>
+        <v>-0.0667</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.117</v>
+        <v>-0.5288</v>
       </c>
       <c r="V2" t="n">
-        <v>0.0704</v>
+        <v>1.4737</v>
       </c>
       <c r="W2" t="n">
-        <v>1.1367</v>
+        <v>1.4737</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.0663</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. MUNOZ MENDOZA</t>
+          <t>J. MUNOZ LEIVA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.9972</v>
+        <v>3.3845</v>
       </c>
       <c r="E3" t="n">
-        <v>3.1825</v>
+        <v>2.6882</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8147</v>
+        <v>0.6962</v>
       </c>
       <c r="G3" t="n">
-        <v>1.0783</v>
+        <v>0.1085</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9119</v>
+        <v>1.5016</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1664</v>
+        <v>-1.393</v>
       </c>
       <c r="J3" t="n">
-        <v>1.3247</v>
+        <v>0.3831</v>
       </c>
       <c r="K3" t="n">
-        <v>1.8431</v>
+        <v>0.0616</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.5184</v>
+        <v>0.3214</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.2463</v>
+        <v>-0.2745</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.9312</v>
+        <v>1.4399</v>
       </c>
       <c r="O3" t="n">
-        <v>0.6848</v>
+        <v>-1.7144</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>2.3787</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.9911</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>0.9911</v>
+        <v>2.3787</v>
       </c>
       <c r="S3" t="n">
-        <v>2.3153</v>
+        <v>0.8268</v>
       </c>
       <c r="T3" t="n">
-        <v>1.9788</v>
+        <v>1.1685</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3365</v>
+        <v>-0.3416</v>
       </c>
       <c r="V3" t="n">
-        <v>0.6036</v>
+        <v>0.0704</v>
       </c>
       <c r="W3" t="n">
-        <v>0.8701</v>
+        <v>1.1367</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.2666</v>
+        <v>-1.0663</v>
       </c>
     </row>
     <row r="4">
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>P. RODRIGUEZ SANCHEZ</t>
+          <t>J. MUNOZ MENDOZA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.8485</v>
+        <v>2.4868</v>
       </c>
       <c r="E5" t="n">
-        <v>2.4622</v>
+        <v>1.7563</v>
       </c>
       <c r="F5" t="n">
-        <v>0.3863</v>
+        <v>0.7305</v>
       </c>
       <c r="G5" t="n">
-        <v>2.8291</v>
+        <v>1.0783</v>
       </c>
       <c r="H5" t="n">
-        <v>0.715</v>
+        <v>0.9119</v>
       </c>
       <c r="I5" t="n">
-        <v>2.1141</v>
+        <v>0.1664</v>
       </c>
       <c r="J5" t="n">
-        <v>3.9029</v>
+        <v>1.3247</v>
       </c>
       <c r="K5" t="n">
-        <v>0.7534999999999999</v>
+        <v>1.8431</v>
       </c>
       <c r="L5" t="n">
-        <v>3.1494</v>
+        <v>-0.5184</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.0738</v>
+        <v>-0.2463</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.0385</v>
+        <v>-0.9312</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.0353</v>
+        <v>0.6848</v>
       </c>
       <c r="P5" t="n">
-        <v>1.784</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
         <v>-0.9911</v>
       </c>
       <c r="R5" t="n">
-        <v>2.7751</v>
+        <v>0.9911</v>
       </c>
       <c r="S5" t="n">
-        <v>-3.2383</v>
+        <v>0.8048999999999999</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.9233</v>
+        <v>0.5526</v>
       </c>
       <c r="U5" t="n">
-        <v>-1.315</v>
+        <v>0.2523</v>
       </c>
       <c r="V5" t="n">
-        <v>1.4737</v>
+        <v>0.6036</v>
       </c>
       <c r="W5" t="n">
-        <v>1.4737</v>
+        <v>0.8701</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-0.2666</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>P. IBANEZ FIDALGO</t>
+          <t>P. CARRASCO LOBO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.4484</v>
+        <v>1.8118</v>
       </c>
       <c r="E6" t="n">
-        <v>0.4576</v>
+        <v>-0.0785</v>
       </c>
       <c r="F6" t="n">
-        <v>1.9908</v>
+        <v>1.8903</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.576</v>
+        <v>0.1553</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1452</v>
+        <v>-0.8893</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.7211</v>
+        <v>1.0446</v>
       </c>
       <c r="J6" t="n">
-        <v>0.2301</v>
+        <v>0.1168</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.3557</v>
+        <v>-1.1767</v>
       </c>
       <c r="L6" t="n">
-        <v>0.5858</v>
+        <v>1.2935</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.806</v>
+        <v>0.0385</v>
       </c>
       <c r="N6" t="n">
-        <v>0.5009</v>
+        <v>0.2874</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.3069</v>
+        <v>-0.2488</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>0.1982</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.9733</v>
+        <v>-0.9911</v>
       </c>
       <c r="R6" t="n">
-        <v>2.9733</v>
+        <v>1.1893</v>
       </c>
       <c r="S6" t="n">
-        <v>2.2246</v>
+        <v>1.4582</v>
       </c>
       <c r="T6" t="n">
-        <v>2.4011</v>
+        <v>0.7958</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1765</v>
+        <v>0.6624</v>
       </c>
       <c r="V6" t="n">
-        <v>0.7997</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>0.7997</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>P. CARRASCO LOBO</t>
+          <t>P. IBANEZ FIDALGO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,64 +955,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>2.2234</v>
+        <v>1.0699</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1647</v>
+        <v>-0.6401</v>
       </c>
       <c r="F7" t="n">
-        <v>2.0587</v>
+        <v>1.71</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1553</v>
+        <v>-0.576</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.8893</v>
+        <v>0.1452</v>
       </c>
       <c r="I7" t="n">
-        <v>1.0446</v>
+        <v>-0.7211</v>
       </c>
       <c r="J7" t="n">
-        <v>0.1168</v>
+        <v>0.2301</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.1767</v>
+        <v>-0.3557</v>
       </c>
       <c r="L7" t="n">
-        <v>1.2935</v>
+        <v>0.5858</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0385</v>
+        <v>-0.806</v>
       </c>
       <c r="N7" t="n">
-        <v>0.2874</v>
+        <v>0.5009</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.2488</v>
+        <v>-1.3069</v>
       </c>
       <c r="P7" t="n">
-        <v>0.1982</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.9911</v>
+        <v>-2.9733</v>
       </c>
       <c r="R7" t="n">
-        <v>1.1893</v>
+        <v>2.9733</v>
       </c>
       <c r="S7" t="n">
-        <v>1.8699</v>
+        <v>0.8462</v>
       </c>
       <c r="T7" t="n">
-        <v>1.039</v>
+        <v>1.3034</v>
       </c>
       <c r="U7" t="n">
-        <v>0.8309</v>
+        <v>-0.4573</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>0.7997</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>0.7997</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. MUÑOZ MENDOZA</t>
+          <t>J. RAMOS ANGULO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6027</v>
+        <v>0.9467</v>
       </c>
       <c r="E8" t="n">
-        <v>0.6027</v>
+        <v>-0.4877</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>1.4343</v>
       </c>
       <c r="G8" t="n">
-        <v>0.6027</v>
+        <v>0.2495</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>-0.2653</v>
       </c>
       <c r="I8" t="n">
-        <v>0.6027</v>
+        <v>0.5148</v>
       </c>
       <c r="J8" t="n">
-        <v>0.6027</v>
+        <v>-0.1209</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>-0.6186</v>
       </c>
       <c r="L8" t="n">
-        <v>0.6027</v>
+        <v>0.4977</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>0.3704</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>0.3533</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>0.0171</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>0.5947</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-0.9911</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.5858</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>-0.5011</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>-0.2458</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>-0.2553</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>0.6036</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>0.8701</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-0.2666</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. MUÑOZ LEIVA</t>
+          <t>J. MUÑOZ MENDOZA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,31 +1111,31 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.3027</v>
+        <v>0.6027</v>
       </c>
       <c r="E9" t="n">
-        <v>0.3027</v>
+        <v>0.6027</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>0.3027</v>
+        <v>0.6027</v>
       </c>
       <c r="H9" t="n">
-        <v>0.3027</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>0.6027</v>
       </c>
       <c r="J9" t="n">
-        <v>0.3027</v>
+        <v>0.6027</v>
       </c>
       <c r="K9" t="n">
-        <v>0.3027</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>0.6027</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. RAMOS ANGULO</t>
+          <t>J. MUÑOZ LEIVA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.2378</v>
+        <v>0.3027</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.365</v>
+        <v>0.3027</v>
       </c>
       <c r="F10" t="n">
-        <v>1.6028</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>0.2495</v>
+        <v>0.3027</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.2653</v>
+        <v>0.3027</v>
       </c>
       <c r="I10" t="n">
-        <v>0.5148</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.1209</v>
+        <v>0.3027</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.6186</v>
+        <v>0.3027</v>
       </c>
       <c r="L10" t="n">
-        <v>0.4977</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>0.3704</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>0.3533</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>0.0171</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>0.5947</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.9911</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.5858</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.21</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.1232</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0868</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>0.6036</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>0.8701</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.2666</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.9215</v>
+        <v>-0.5607</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.7225</v>
+        <v>-0.5583</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.199</v>
+        <v>-0.0024</v>
       </c>
       <c r="G11" t="n">
         <v>-1.1421</v>
@@ -1312,13 +1312,13 @@
         <v>0.5947</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.1075</v>
+        <v>0.2533</v>
       </c>
       <c r="T11" t="n">
-        <v>0.3047</v>
+        <v>0.469</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.4123</v>
+        <v>-0.2157</v>
       </c>
       <c r="V11" t="n">
         <v>-0.2666</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.027</v>
+        <v>-0.9708</v>
       </c>
       <c r="E12" t="n">
         <v>-0.9932</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.0338</v>
+        <v>0.0223</v>
       </c>
       <c r="G12" t="n">
         <v>-0.2715</v>
@@ -1390,13 +1390,13 @@
         <v>0.1982</v>
       </c>
       <c r="S12" t="n">
-        <v>0.0374</v>
+        <v>0.0936</v>
       </c>
       <c r="T12" t="n">
         <v>-0.0624</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0998</v>
+        <v>0.156</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,10 +1423,10 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.8004</v>
+        <v>-2.3929</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.5631</v>
+        <v>-2.1556</v>
       </c>
       <c r="F13" t="n">
         <v>-0.2373</v>
@@ -1468,10 +1468,10 @@
         <v>0.1982</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.2203</v>
+        <v>0.1872</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.301</v>
+        <v>0.1065</v>
       </c>
       <c r="U13" t="n">
         <v>0.08069999999999999</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-4.3756</v>
+        <v>-4.3341</v>
       </c>
       <c r="E14" t="n">
-        <v>-3.8577</v>
+        <v>-3.5916</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.5179</v>
+        <v>-0.7425</v>
       </c>
       <c r="G14" t="n">
         <v>-2.6746</v>
@@ -1546,13 +1546,13 @@
         <v>2.9733</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.036</v>
+        <v>0.0055</v>
       </c>
       <c r="T14" t="n">
-        <v>0.2389</v>
+        <v>0.505</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.2749</v>
+        <v>-0.4995</v>
       </c>
       <c r="V14" t="n">
         <v>-0.674</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-5.6664</v>
+        <v>-4.9428</v>
       </c>
       <c r="E15" t="n">
-        <v>-5.1256</v>
+        <v>-4.5144</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.5407</v>
+        <v>-0.4284</v>
       </c>
       <c r="G15" t="n">
         <v>-5.1754</v>
@@ -1624,13 +1624,13 @@
         <v>0.9911</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.707</v>
+        <v>0.0165</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.4368</v>
+        <v>0.1744</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.2702</v>
+        <v>-0.1579</v>
       </c>
       <c r="V15" t="n">
         <v>1.2071</v>
@@ -1657,10 +1657,10 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>5.289599999999997</v>
+        <v>5.9138</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.9557000000000002</v>
+        <v>-0.3320000000000007</v>
       </c>
       <c r="F16" t="n">
         <v>6.2455</v>
@@ -1672,7 +1672,7 @@
         <v>-2.017599999999999</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.05690000000000017</v>
+        <v>-0.05690000000000106</v>
       </c>
       <c r="J16" t="n">
         <v>0.5296999999999987</v>
@@ -1702,13 +1702,13 @@
         <v>16.8488</v>
       </c>
       <c r="S16" t="n">
-        <v>2.771600000000001</v>
+        <v>3.3956</v>
       </c>
       <c r="T16" t="n">
-        <v>4.076300000000001</v>
+        <v>4.700299999999999</v>
       </c>
       <c r="U16" t="n">
-        <v>-1.3048</v>
+        <v>-1.3047</v>
       </c>
       <c r="V16" t="n">
         <v>2.6104</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>3.5801</v>
+        <v>2.5392</v>
       </c>
       <c r="E17" t="n">
-        <v>4.4801</v>
+        <v>3.3596</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.9</v>
+        <v>-0.8203</v>
       </c>
       <c r="G17" t="n">
         <v>2.1655</v>
@@ -1780,13 +1780,13 @@
         <v>0.5947</v>
       </c>
       <c r="S17" t="n">
-        <v>1.4236</v>
+        <v>0.3827</v>
       </c>
       <c r="T17" t="n">
-        <v>1.4758</v>
+        <v>0.3553</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.0523</v>
+        <v>0.0274</v>
       </c>
       <c r="V17" t="n">
         <v>-0.6036</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>T. WOLKOWYSKI</t>
+          <t>F. MONTIEL RODRIGUEZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>3.1515</v>
+        <v>1.292</v>
       </c>
       <c r="E18" t="n">
-        <v>2.3593</v>
+        <v>1.3821</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7922</v>
+        <v>-0.0901</v>
       </c>
       <c r="G18" t="n">
-        <v>2.7457</v>
+        <v>3.2686</v>
       </c>
       <c r="H18" t="n">
-        <v>1.3952</v>
+        <v>2.3313</v>
       </c>
       <c r="I18" t="n">
-        <v>1.3505</v>
+        <v>0.9373</v>
       </c>
       <c r="J18" t="n">
-        <v>1.8712</v>
+        <v>2.947</v>
       </c>
       <c r="K18" t="n">
-        <v>0.4248</v>
+        <v>2.1797</v>
       </c>
       <c r="L18" t="n">
-        <v>1.4464</v>
+        <v>0.7673</v>
       </c>
       <c r="M18" t="n">
-        <v>0.8745000000000001</v>
+        <v>0.3216</v>
       </c>
       <c r="N18" t="n">
-        <v>0.9704</v>
+        <v>0.1515</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.0959</v>
+        <v>0.17</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.7929</v>
+        <v>0.1982</v>
       </c>
       <c r="Q18" t="n">
-        <v>-3.1716</v>
+        <v>-1.1893</v>
       </c>
       <c r="R18" t="n">
-        <v>2.3787</v>
+        <v>1.3876</v>
       </c>
       <c r="S18" t="n">
-        <v>3.3463</v>
+        <v>0.2394</v>
       </c>
       <c r="T18" t="n">
-        <v>2.8599</v>
+        <v>0.2984</v>
       </c>
       <c r="U18" t="n">
-        <v>0.4864</v>
+        <v>-0.0589</v>
       </c>
       <c r="V18" t="n">
-        <v>-2.1476</v>
+        <v>-2.4142</v>
       </c>
       <c r="W18" t="n">
-        <v>0.7997</v>
+        <v>-0.674</v>
       </c>
       <c r="X18" t="n">
-        <v>-2.9474</v>
+        <v>-1.7403</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>F. MONTIEL RODRIGUEZ</t>
+          <t>R. VIDALES MOLINA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.9629</v>
+        <v>1.0531</v>
       </c>
       <c r="E19" t="n">
-        <v>1.0765</v>
+        <v>-2.4219</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.1136</v>
+        <v>3.4749</v>
       </c>
       <c r="G19" t="n">
-        <v>3.2686</v>
+        <v>-2.18</v>
       </c>
       <c r="H19" t="n">
-        <v>2.3313</v>
+        <v>-0.2515</v>
       </c>
       <c r="I19" t="n">
-        <v>0.9373</v>
+        <v>-1.9285</v>
       </c>
       <c r="J19" t="n">
-        <v>2.947</v>
+        <v>-3.1903</v>
       </c>
       <c r="K19" t="n">
-        <v>2.1797</v>
+        <v>-1.3577</v>
       </c>
       <c r="L19" t="n">
-        <v>0.7673</v>
+        <v>-1.8326</v>
       </c>
       <c r="M19" t="n">
-        <v>0.3216</v>
+        <v>1.0103</v>
       </c>
       <c r="N19" t="n">
-        <v>0.1515</v>
+        <v>1.1062</v>
       </c>
       <c r="O19" t="n">
-        <v>0.17</v>
+        <v>-0.0959</v>
       </c>
       <c r="P19" t="n">
-        <v>0.1982</v>
+        <v>-0.3964</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.1893</v>
+        <v>-2.9733</v>
       </c>
       <c r="R19" t="n">
-        <v>1.3876</v>
+        <v>2.5769</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.0897</v>
+        <v>-0.3992</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.0072</v>
+        <v>0.1205</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.0825</v>
+        <v>-0.5197000000000001</v>
       </c>
       <c r="V19" t="n">
-        <v>-2.4142</v>
+        <v>4.0287</v>
       </c>
       <c r="W19" t="n">
-        <v>-0.674</v>
+        <v>3.6213</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.7403</v>
+        <v>0.4074</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>R. VIDALES MOLINA</t>
+          <t>T. WOLKOWYSKI</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.7827</v>
+        <v>0.5421</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.5237</v>
+        <v>0.4238</v>
       </c>
       <c r="F20" t="n">
-        <v>3.3064</v>
+        <v>0.1183</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.18</v>
+        <v>2.7457</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.2515</v>
+        <v>1.3952</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.9285</v>
+        <v>1.3505</v>
       </c>
       <c r="J20" t="n">
-        <v>-3.1903</v>
+        <v>1.8712</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.3577</v>
+        <v>0.4248</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.8326</v>
+        <v>1.4464</v>
       </c>
       <c r="M20" t="n">
-        <v>1.0103</v>
+        <v>0.8745000000000001</v>
       </c>
       <c r="N20" t="n">
-        <v>1.1062</v>
+        <v>0.9704</v>
       </c>
       <c r="O20" t="n">
         <v>-0.0959</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.3964</v>
+        <v>-0.7929</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.9733</v>
+        <v>-3.1716</v>
       </c>
       <c r="R20" t="n">
-        <v>2.5769</v>
+        <v>2.3787</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.6695</v>
+        <v>0.7369</v>
       </c>
       <c r="T20" t="n">
-        <v>0.0186</v>
+        <v>0.9244</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.6882</v>
+        <v>-0.1875</v>
       </c>
       <c r="V20" t="n">
-        <v>4.0287</v>
+        <v>-2.1476</v>
       </c>
       <c r="W20" t="n">
-        <v>3.6213</v>
+        <v>0.7997</v>
       </c>
       <c r="X20" t="n">
-        <v>0.4074</v>
+        <v>-2.9474</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J. RAMIREZ GUERRA-LIBRERO</t>
+          <t>D. TERRÓN FERNÁNDEZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.6792</v>
+        <v>0.3027</v>
       </c>
       <c r="E21" t="n">
-        <v>0.4699</v>
+        <v>0.3027</v>
       </c>
       <c r="F21" t="n">
-        <v>0.2093</v>
+        <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>0.1102</v>
+        <v>0.3027</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.5689</v>
+        <v>0.3027</v>
       </c>
       <c r="I21" t="n">
-        <v>0.6791</v>
+        <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.6388</v>
+        <v>0.3027</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.6388</v>
+        <v>0.3027</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>0.749</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>0.0699</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>0.6791</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>0.1982</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>0.1982</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>0.9743000000000001</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>1.1087</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1344</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.6036</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.6036</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>D. TERRON FERNANDEZ</t>
+          <t>J. RAMIREZ GUERRA-LIBRERO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>0.5003</v>
+        <v>0.2822</v>
       </c>
       <c r="E22" t="n">
-        <v>1.4806</v>
+        <v>-0.0395</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.9802999999999999</v>
+        <v>0.3216</v>
       </c>
       <c r="G22" t="n">
-        <v>4.2132</v>
+        <v>0.1102</v>
       </c>
       <c r="H22" t="n">
-        <v>0.5379</v>
+        <v>-0.5689</v>
       </c>
       <c r="I22" t="n">
-        <v>3.6754</v>
+        <v>0.6791</v>
       </c>
       <c r="J22" t="n">
-        <v>5.1858</v>
+        <v>-0.6388</v>
       </c>
       <c r="K22" t="n">
-        <v>0.9956</v>
+        <v>-0.6388</v>
       </c>
       <c r="L22" t="n">
-        <v>4.1901</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.9725</v>
+        <v>0.749</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.4577</v>
+        <v>0.0699</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.5148</v>
+        <v>0.6791</v>
       </c>
       <c r="P22" t="n">
-        <v>-2.9733</v>
+        <v>0.1982</v>
       </c>
       <c r="Q22" t="n">
-        <v>-3.9645</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>0.9911</v>
+        <v>0.1982</v>
       </c>
       <c r="S22" t="n">
-        <v>0.1306</v>
+        <v>0.5773</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.0072</v>
+        <v>0.5993000000000001</v>
       </c>
       <c r="U22" t="n">
-        <v>0.1378</v>
+        <v>-0.0221</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.8701</v>
+        <v>-0.6036</v>
       </c>
       <c r="W22" t="n">
-        <v>0.2666</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.1367</v>
+        <v>-0.6036</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>D. TERRÓN FERNÁNDEZ</t>
+          <t>D. TERRON FERNANDEZ</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>0.3027</v>
+        <v>0.0393</v>
       </c>
       <c r="E23" t="n">
-        <v>0.3027</v>
+        <v>1.2769</v>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>-1.2376</v>
       </c>
       <c r="G23" t="n">
-        <v>0.3027</v>
+        <v>4.2132</v>
       </c>
       <c r="H23" t="n">
-        <v>0.3027</v>
+        <v>0.5379</v>
       </c>
       <c r="I23" t="n">
-        <v>0</v>
+        <v>3.6754</v>
       </c>
       <c r="J23" t="n">
-        <v>0.3027</v>
+        <v>5.1858</v>
       </c>
       <c r="K23" t="n">
-        <v>0.3027</v>
+        <v>0.9956</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>4.1901</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>-0.9725</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>-0.4577</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>-0.5148</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>-2.9733</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>-3.9645</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>0.9911</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>-0.3304</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>-0.211</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>-0.1195</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>-0.8701</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>0.2666</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>-1.1367</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>P. MORENO VEGA</t>
+          <t>A. MAYOR MARTIN</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,73 +2281,73 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.7096</v>
+        <v>-0.5738</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.1248</v>
+        <v>-2.3627</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.5848</v>
+        <v>1.7889</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.4677</v>
+        <v>-0.2489</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.2018</v>
+        <v>0.5295</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.266</v>
+        <v>-0.7784</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>-1.4763</v>
       </c>
       <c r="K24" t="n">
-        <v>0</v>
+        <v>-1.1899</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>-0.2864</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.4677</v>
+        <v>1.2274</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.2018</v>
+        <v>1.7194</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.266</v>
+        <v>-0.492</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>0.7929</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>-2.1805</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>2.9733</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.2419</v>
+        <v>-1.1178</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.1248</v>
+        <v>-0.1796</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.1171</v>
+        <v>-0.9382</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.4737</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>-1.4737</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A. AGUILAR GARCIA</t>
+          <t>P. MORENO VEGA</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,58 +2359,58 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-1.1067</v>
+        <v>-0.6816</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.7013</v>
+        <v>-0.1248</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.4053</v>
+        <v>-0.5568</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.9709</v>
+        <v>-0.4677</v>
       </c>
       <c r="H25" t="n">
-        <v>0.0699</v>
+        <v>-0.2018</v>
       </c>
       <c r="I25" t="n">
-        <v>-1.0407</v>
+        <v>-0.266</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.639</v>
+        <v>0</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>-0.639</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.3319</v>
+        <v>-0.4677</v>
       </c>
       <c r="N25" t="n">
-        <v>0.0699</v>
+        <v>-0.2018</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.4018</v>
+        <v>-0.266</v>
       </c>
       <c r="P25" t="n">
-        <v>0.1982</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>0.1982</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.334</v>
+        <v>-0.2138</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.0624</v>
+        <v>-0.1248</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.2717</v>
+        <v>-0.089</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -2425,7 +2425,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A. MAYOR MARTIN</t>
+          <t>A. AGUILAR GARCIA</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2437,67 +2437,67 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-2.414</v>
+        <v>-1.0048</v>
       </c>
       <c r="E26" t="n">
-        <v>-3.5852</v>
+        <v>-0.5995</v>
       </c>
       <c r="F26" t="n">
-        <v>1.1712</v>
+        <v>-0.4053</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.2489</v>
+        <v>-0.9709</v>
       </c>
       <c r="H26" t="n">
-        <v>0.5295</v>
+        <v>0.0699</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.7784</v>
+        <v>-1.0407</v>
       </c>
       <c r="J26" t="n">
-        <v>-1.4763</v>
+        <v>-0.639</v>
       </c>
       <c r="K26" t="n">
-        <v>-1.1899</v>
+        <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>-0.2864</v>
+        <v>-0.639</v>
       </c>
       <c r="M26" t="n">
-        <v>1.2274</v>
+        <v>-0.3319</v>
       </c>
       <c r="N26" t="n">
-        <v>1.7194</v>
+        <v>0.0699</v>
       </c>
       <c r="O26" t="n">
-        <v>-0.492</v>
+        <v>-0.4018</v>
       </c>
       <c r="P26" t="n">
-        <v>0.7929</v>
+        <v>0.1982</v>
       </c>
       <c r="Q26" t="n">
-        <v>-2.1805</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>2.9733</v>
+        <v>0.1982</v>
       </c>
       <c r="S26" t="n">
-        <v>-2.958</v>
+        <v>-0.2322</v>
       </c>
       <c r="T26" t="n">
-        <v>-1.402</v>
+        <v>0.0395</v>
       </c>
       <c r="U26" t="n">
-        <v>-1.5559</v>
+        <v>-0.2717</v>
       </c>
       <c r="V26" t="n">
         <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>1.4737</v>
+        <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>-1.4737</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-2.7861</v>
+        <v>-2.1586</v>
       </c>
       <c r="E27" t="n">
-        <v>-2.0373</v>
+        <v>-1.6299</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.7488</v>
+        <v>-0.5286999999999999</v>
       </c>
       <c r="G27" t="n">
         <v>-1.3923</v>
@@ -2560,13 +2560,13 @@
         <v>0.3964</v>
       </c>
       <c r="S27" t="n">
-        <v>-0.6009</v>
+        <v>0.0266</v>
       </c>
       <c r="T27" t="n">
-        <v>-0.2496</v>
+        <v>0.1579</v>
       </c>
       <c r="U27" t="n">
-        <v>-0.3513</v>
+        <v>-0.1313</v>
       </c>
       <c r="V27" t="n">
         <v>0</v>
@@ -2581,7 +2581,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>E. LOPEZ GARCIA</t>
+          <t>N. ESCOLANO ZAVALA</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2593,73 +2593,73 @@
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>-4.0808</v>
+        <v>-2.762</v>
       </c>
       <c r="E28" t="n">
-        <v>-4.8522</v>
+        <v>-1.6732</v>
       </c>
       <c r="F28" t="n">
-        <v>0.7714</v>
+        <v>-1.0888</v>
       </c>
       <c r="G28" t="n">
-        <v>-4.0751</v>
+        <v>-1.3962</v>
       </c>
       <c r="H28" t="n">
-        <v>-2.7358</v>
+        <v>0.1708</v>
       </c>
       <c r="I28" t="n">
-        <v>-1.3393</v>
+        <v>-1.5669</v>
       </c>
       <c r="J28" t="n">
-        <v>-3.8534</v>
+        <v>-0.3106</v>
       </c>
       <c r="K28" t="n">
-        <v>-3.2948</v>
+        <v>-0.3223</v>
       </c>
       <c r="L28" t="n">
-        <v>-0.5586</v>
+        <v>0.0117</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.2217</v>
+        <v>-1.0855</v>
       </c>
       <c r="N28" t="n">
-        <v>0.5590000000000001</v>
+        <v>0.4931</v>
       </c>
       <c r="O28" t="n">
-        <v>-0.7806999999999999</v>
+        <v>-1.5786</v>
       </c>
       <c r="P28" t="n">
-        <v>0.3964</v>
+        <v>0.5947</v>
       </c>
       <c r="Q28" t="n">
-        <v>-0.9911</v>
+        <v>-1.1893</v>
       </c>
       <c r="R28" t="n">
-        <v>1.3876</v>
+        <v>1.784</v>
       </c>
       <c r="S28" t="n">
-        <v>-1.6093</v>
+        <v>-0.7534</v>
       </c>
       <c r="T28" t="n">
-        <v>-1.2149</v>
+        <v>-0.1732</v>
       </c>
       <c r="U28" t="n">
-        <v>-0.3944</v>
+        <v>-0.5802</v>
       </c>
       <c r="V28" t="n">
-        <v>1.2071</v>
+        <v>-1.2071</v>
       </c>
       <c r="W28" t="n">
-        <v>1.2071</v>
+        <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>-1.2071</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>N. ESCOLANO ZAVALA</t>
+          <t>E. LOPEZ GARCIA</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2671,67 +2671,67 @@
         <v>1</v>
       </c>
       <c r="D29" t="n">
-        <v>-4.1516</v>
+        <v>-3.4801</v>
       </c>
       <c r="E29" t="n">
-        <v>-2.59</v>
+        <v>-4.1391</v>
       </c>
       <c r="F29" t="n">
-        <v>-1.5616</v>
+        <v>0.6591</v>
       </c>
       <c r="G29" t="n">
-        <v>-1.3962</v>
+        <v>-4.0751</v>
       </c>
       <c r="H29" t="n">
-        <v>0.1708</v>
+        <v>-2.7358</v>
       </c>
       <c r="I29" t="n">
-        <v>-1.5669</v>
+        <v>-1.3393</v>
       </c>
       <c r="J29" t="n">
-        <v>-0.3106</v>
+        <v>-3.8534</v>
       </c>
       <c r="K29" t="n">
-        <v>-0.3223</v>
+        <v>-3.2948</v>
       </c>
       <c r="L29" t="n">
-        <v>0.0117</v>
+        <v>-0.5586</v>
       </c>
       <c r="M29" t="n">
-        <v>-1.0855</v>
+        <v>-0.2217</v>
       </c>
       <c r="N29" t="n">
-        <v>0.4931</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="O29" t="n">
-        <v>-1.5786</v>
+        <v>-0.7806999999999999</v>
       </c>
       <c r="P29" t="n">
-        <v>0.5947</v>
+        <v>0.3964</v>
       </c>
       <c r="Q29" t="n">
-        <v>-1.1893</v>
+        <v>-0.9911</v>
       </c>
       <c r="R29" t="n">
-        <v>1.784</v>
+        <v>1.3876</v>
       </c>
       <c r="S29" t="n">
-        <v>-2.143</v>
+        <v>-1.0085</v>
       </c>
       <c r="T29" t="n">
-        <v>-1.0901</v>
+        <v>-0.5018</v>
       </c>
       <c r="U29" t="n">
-        <v>-1.053</v>
+        <v>-0.5068</v>
       </c>
       <c r="V29" t="n">
-        <v>-1.2071</v>
+        <v>1.2071</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>1.2071</v>
       </c>
       <c r="X29" t="n">
-        <v>-1.2071</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -2749,31 +2749,31 @@
         <v>1</v>
       </c>
       <c r="D30" t="n">
-        <v>-5.289399999999999</v>
+        <v>-4.610300000000001</v>
       </c>
       <c r="E30" t="n">
-        <v>-6.245399999999998</v>
+        <v>-6.2455</v>
       </c>
       <c r="F30" t="n">
-        <v>0.9560999999999995</v>
+        <v>1.6352</v>
       </c>
       <c r="G30" t="n">
         <v>2.074799999999999</v>
       </c>
       <c r="H30" t="n">
-        <v>2.017800000000001</v>
+        <v>2.0178</v>
       </c>
       <c r="I30" t="n">
-        <v>0.0571999999999997</v>
+        <v>0.05720000000000014</v>
       </c>
       <c r="J30" t="n">
-        <v>2.604200000000002</v>
+        <v>2.604199999999999</v>
       </c>
       <c r="K30" t="n">
         <v>-2.5438</v>
       </c>
       <c r="L30" t="n">
-        <v>5.148000000000001</v>
+        <v>5.148</v>
       </c>
       <c r="M30" t="n">
         <v>-0.5291999999999997</v>
@@ -2782,10 +2782,10 @@
         <v>4.5616</v>
       </c>
       <c r="O30" t="n">
-        <v>-5.091</v>
+        <v>-5.090999999999999</v>
       </c>
       <c r="P30" t="n">
-        <v>-1.9822</v>
+        <v>-1.982200000000001</v>
       </c>
       <c r="Q30" t="n">
         <v>-16.8489</v>
@@ -2794,13 +2794,13 @@
         <v>14.8667</v>
       </c>
       <c r="S30" t="n">
-        <v>-2.7715</v>
+        <v>-2.0924</v>
       </c>
       <c r="T30" t="n">
-        <v>1.3048</v>
+        <v>1.3049</v>
       </c>
       <c r="U30" t="n">
-        <v>-4.0766</v>
+        <v>-3.3975</v>
       </c>
       <c r="V30" t="n">
         <v>-2.610400000000001</v>
@@ -2809,7 +2809,7 @@
         <v>6.6944</v>
       </c>
       <c r="X30" t="n">
-        <v>-9.305</v>
+        <v>-9.305000000000001</v>
       </c>
     </row>
   </sheetData>
